--- a/apps/frontend/public/templates/bulk-import-template.xlsx
+++ b/apps/frontend/public/templates/bulk-import-template.xlsx
@@ -2,56 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R8841e7cb7c534fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="2" r:id="R53a60a6e498948ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R29e3624126d74146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Ree8a964ffa39408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="2" r:id="Rdfd36d7c19f64da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R14b7a338641343be"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">Drug Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Generic Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Strength</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dosage Form</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unit</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Quantity</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Expiry Date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Paracetamol</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">500mg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tablet</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tablets</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="100" formatCode="YYYY-MM-DD"/>
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -76,7 +43,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="8">
     <x:xf/>
     <x:xf fontId="1" applyFont="1"/>
     <x:xf numFmtId="100" applyNumberFormat="1"/>
@@ -88,6 +55,7 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0"/>
     <x:xf numFmtId="200" xfId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <x:xf numFmtId="201" xfId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -294,8 +262,8 @@
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -316,12 +284,14 @@
         <x:v>Unit</x:v>
       </x:c>
       <x:c r="F1" s="1" t="str">
+        <x:v>Low Stock Threshold</x:v>
+      </x:c>
+      <x:c r="G1" s="5" t="str">
         <x:v>Quantity</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="H1" t="str">
         <x:v>Expiry Date</x:v>
       </x:c>
-      <x:c r="H1"/>
     </x:row>
     <x:row r="2">
       <x:c r="G2" s="6"/>
@@ -6336,82 +6306,88 @@
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+      <x:c r="A1" s="1" t="str">
+        <x:v>Drug Name</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+      <x:c r="B1" s="1" t="str">
+        <x:v>Generic Name</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
+      <x:c r="C1" s="1" t="str">
+        <x:v>Strength</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
+      <x:c r="D1" s="1" t="str">
+        <x:v>Dosage Form</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
+      <x:c r="E1" s="1" t="str">
+        <x:v>Unit</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
+      <x:c r="F1" s="1" t="str">
+        <x:v>Low Stock Threshold</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="s">
-        <x:v>6</x:v>
+      <x:c r="G1" s="5" t="str">
+        <x:v>Quantity</x:v>
       </x:c>
-      <x:c r="H1"/>
+      <x:c r="H1" t="str">
+        <x:v>Expiry Date</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="s">
-        <x:v>7</x:v>
+      <x:c r="A2" t="str">
+        <x:v>Paracetamol</x:v>
       </x:c>
-      <x:c r="B2" t="s">
-        <x:v>7</x:v>
+      <x:c r="B2" t="str">
+        <x:v>Paracetamol</x:v>
       </x:c>
-      <x:c r="C2" t="s">
-        <x:v>8</x:v>
+      <x:c r="C2" t="str">
+        <x:v>500mg</x:v>
       </x:c>
-      <x:c r="D2" t="s">
-        <x:v>9</x:v>
+      <x:c r="D2" t="str">
+        <x:v>Tablet</x:v>
       </x:c>
-      <x:c r="E2" t="s">
-        <x:v>10</x:v>
+      <x:c r="E2" t="str">
+        <x:v>Tablets</x:v>
       </x:c>
-      <x:c r="F2">
+      <x:c r="F2" s="7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="G2" s="6">
+      <x:c r="H2" s="6" t="n">
         <x:v>46568</x:v>
       </x:c>
-      <x:c r="H2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="s">
-        <x:v>7</x:v>
+      <x:c r="A3" t="str">
+        <x:v>Paracetamol</x:v>
       </x:c>
-      <x:c r="B3" t="s">
-        <x:v>7</x:v>
+      <x:c r="B3" t="str">
+        <x:v>Paracetamol</x:v>
       </x:c>
-      <x:c r="C3" t="s">
-        <x:v>8</x:v>
+      <x:c r="C3" t="str">
+        <x:v>500mg</x:v>
       </x:c>
-      <x:c r="D3" t="s">
-        <x:v>9</x:v>
+      <x:c r="D3" t="str">
+        <x:v>Tablet</x:v>
       </x:c>
-      <x:c r="E3" t="s">
-        <x:v>10</x:v>
+      <x:c r="E3" t="str">
+        <x:v>Tablets</x:v>
       </x:c>
-      <x:c r="F3">
+      <x:c r="F3" s="7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G3" s="6">
+      <x:c r="H3" s="6" t="n">
         <x:v>46752</x:v>
       </x:c>
-      <x:c r="H3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -6423,13 +6399,13 @@
       <x:c r="C4"/>
       <x:c r="D4"/>
       <x:c r="E4"/>
-      <x:c r="F4" t="n">
+      <x:c r="F4" s="7"/>
+      <x:c r="G4" s="7" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="G4" s="6" t="n">
+      <x:c r="H4" s="6" t="n">
         <x:v>46583</x:v>
       </x:c>
-      <x:c r="H4"/>
     </x:row>
     <x:row r="5">
       <x:c r="G5" s="6"/>
@@ -12433,12 +12409,12 @@
     <x:col min="1" max="1" width="100" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="3" t="str">
         <x:v>Bulk Import Instructions</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="4"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -12458,7 +12434,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>4. Optional columns: Strength, Dosage Form, Unit - columns may be omitted in CSV files or cells left blank.</x:v>
+        <x:v>4. Optional columns: Strength, Dosage Form, Unit, Low Stock Threshold - columns may be omitted in CSV files or cells left blank.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -12468,36 +12444,38 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="4" t="str">
-        <x:v>6. Expiry Date must be today or later. Use the YYYY-MM-DD format.</x:v>
+        <x:v>6. Low Stock Threshold must be a whole number of zero or more when supplied.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="4" t="str">
-        <x:v>7. Incomplete drug details are matched by Drug Name and Generic Name. Supply optional details when more than one Drug Master record could match.</x:v>
+        <x:v>7. Expiry Date must be today or later. Use the YYYY-MM-DD format.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A10" s="4" t="str">
-        <x:v>8. The same drug can appear on multiple rows when stock belongs to separate batches.</x:v>
+        <x:v>8. Incomplete drug details are matched by Drug Name and Generic Name. Supply optional details when more than one Drug Master record could match.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="4" t="str">
-        <x:v>9. Exact duplicate rows will be rejected - remove or correct them before importing.</x:v>
+        <x:v>9. A supplied Low Stock Threshold updates a matching drug. A blank cell preserves its existing threshold or uses the workspace default for a new drug.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="4" t="str">
-        <x:v>10. Completely empty rows are ignored. The file must not exceed 10 MB or 2,000 filled-in rows.</x:v>
+        <x:v>10. The same drug can appear on multiple rows when stock belongs to separate batches.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>11. Supported file types: .xlsx and .csv (legacy .xls is not supported).</x:v>
+        <x:v>11. Exact duplicate rows will be rejected - remove or correct them before importing.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="4"/>
+      <x:c r="A14" s="4" t="str">
+        <x:v>12. Completely empty rows are ignored. The file must not exceed 10 MB or 2,000 filled-in rows. Supported file types: .xlsx and .csv.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/apps/frontend/public/templates/bulk-import-template.xlsx
+++ b/apps/frontend/public/templates/bulk-import-template.xlsx
@@ -265,6 +265,9 @@
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -292,6 +295,15 @@
       <x:c r="H1" t="str">
         <x:v>Expiry Date</x:v>
       </x:c>
+      <x:c r="I1" s="1" t="str">
+        <x:v>Cost Price ₦ (per unit)</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="str">
+        <x:v>Retail Price ₦ (per unit)</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="str">
+        <x:v>Wholesale Price ₦ (per unit)</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="G2" s="6"/>
@@ -6309,6 +6321,9 @@
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -6336,6 +6351,15 @@
       <x:c r="H1" t="str">
         <x:v>Expiry Date</x:v>
       </x:c>
+      <x:c r="I1" s="1" t="str">
+        <x:v>Cost Price ₦ (per unit)</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="str">
+        <x:v>Retail Price ₦ (per unit)</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="str">
+        <x:v>Wholesale Price ₦ (per unit)</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -6362,6 +6386,15 @@
       <x:c r="H2" s="6" t="n">
         <x:v>46568</x:v>
       </x:c>
+      <x:c r="I2" t="n">
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="J2" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="K2" t="n">
+        <x:v>1400</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -6388,6 +6421,15 @@
       <x:c r="H3" s="6" t="n">
         <x:v>46752</x:v>
       </x:c>
+      <x:c r="I3" t="n">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="J3" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="K3" t="n">
+        <x:v>1400</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -12434,7 +12476,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>4. Optional columns: Strength, Dosage Form, Unit, Low Stock Threshold - columns may be omitted in CSV files or cells left blank.</x:v>
+        <x:v>4. Optional columns: Strength, Dosage Form, Unit, Low Stock Threshold, Cost Price ₦ (per unit), Retail Price ₦ (per unit), Wholesale Price ₦ (per unit) - columns may be omitted in CSV files or cells left blank.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -12477,6 +12519,16 @@
         <x:v>12. Completely empty rows are ignored. The file must not exceed 10 MB or 2,000 filled-in rows. Supported file types: .xlsx and .csv.</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="4" t="str">
+        <x:v>13. Every price is for one of the drug's Unit (per strip if the Unit is Strips). Commas and the ₦ sign are fine: ₦1,500 is read as 1500.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="4" t="str">
+        <x:v>14. Cost Price is what you paid for this delivery. Retail and Wholesale Price belong to the drug: a price in this file replaces the drug's current price, and the import summary lists what changed.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
